--- a/04_DataDictionary/DataDictionary_Hotel.xlsx
+++ b/04_DataDictionary/DataDictionary_Hotel.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>role — Роль: Роли сотрудников</t>
+          <t>floor — Этаж: Этажи гостиницы</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -529,17 +529,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>INT IDENTITY</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -555,24 +555,24 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор роли</t>
+          <t>Идентификатор этажа</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>SMALLINT</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Администратор / Руководитель / Горничная</t>
+          <t>Номер этажа (&gt; 0)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>employee — Сотрудник (пользователь): Сотрудники гостиницы; у кого есть логин — пользователи приложения</t>
+          <t>comfort_class — Класс комфорта: Стандарт, Эконом, Бюджет, Бизнес, Студия, Люкс</t>
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>comfort_class</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>INT IDENTITY</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -634,36 +634,32 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор сотрудника</t>
+          <t>Идентификатор класса</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>comfort_class</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>role.role_id</t>
-        </is>
-      </c>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -671,56 +667,44 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Роль</t>
+          <t>Название класса</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Фамилия</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>bed_type — Тип кроватей: Конфигурация кроватей</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>first_name</t>
+          <t>bed_type</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -729,19 +713,19 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Имя</t>
+          <t>Идентификатор типа</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>bed_type</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>middle_name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -749,127 +733,115 @@
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Отчество</t>
+          <t>Например «1 или 2 кровати»</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>bed_type</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>beds_min</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Логин (у горничных пусто — в приложение не входят)</t>
+          <t>Минимум кроватей</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>bed_type</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>password_hash</t>
+          <t>beds_max</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>SMALLINT</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Хэш пароля SHA-256</t>
+          <t>Максимум кроватей (≥ beds_min)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>is_blocked</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Заблокирован (3 ошибки входа или месяц без входа)</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>room_category — Категория номера: Категории из «Номерной фонд.xlsx», разобранные на признаки</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>failed_attempts</t>
+          <t>room_category</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -878,27 +850,31 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Неудачных попыток входа подряд</t>
+          <t>Идентификатор категории</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>room_category</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>must_change_password</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -907,51 +883,75 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Сменить выданный пароль при первом входе</t>
+          <t>Название категории</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>room_category</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>last_login_at</t>
+          <t>comfort_class_id</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>comfort_class.id</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Класс комфорта</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>room_category</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Последний успешный вход</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>room_category — Категория номера: Категории номеров</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="3" t="n"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Вместимость (не указана заказчиком для Бизнес, Студия, Люкс)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -959,21 +959,17 @@
           <t>room_category</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>room_category_id</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>rooms_count</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -982,7 +978,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор категории</t>
+          <t>Число комнат в номере</t>
         </is>
       </c>
     </row>
@@ -994,35 +990,39 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>bed_type_id</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>bed_type.id</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Название категории из «Номерной фонд.xlsx»</t>
+          <t>Тип кроватей</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>room_status — Статус номера: Состояния номера</t>
+          <t>room — Номер: Номерной фонд</t>
         </is>
       </c>
       <c r="B20" s="3" t="n"/>
@@ -1035,17 +1035,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>room_status</t>
+          <t>room</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>room_status_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>INT IDENTITY</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1061,24 +1061,24 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор статуса</t>
+          <t>Идентификатор номера</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>room_status</t>
+          <t>room</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>number</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1094,22 +1094,46 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Чистый / Занят / Грязный / Назначен к уборке</t>
+          <t>Номер комнаты (101)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>room — Номер: Номерной фонд</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="3" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>room</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>floor_id</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>floor.id</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Этаж</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1117,22 +1141,26 @@
           <t>room</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>room_id</t>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>category_id</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>room_category.id</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1140,60 +1168,44 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор номера</t>
+          <t>Категория</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>room</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Номер комнаты (101)</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>room_status — Статус номера: Состояния номера</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>room</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>floor</t>
+          <t>room_status</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
@@ -1202,36 +1214,32 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Этаж</t>
+          <t>Идентификатор статуса</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>room</t>
+          <t>room_status</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>room_category_id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>room_category.room_category_id</t>
-        </is>
-      </c>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1239,82 +1247,82 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Категория</t>
+          <t>Занят / Чистый / Назначен к уборке / Грязный</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>room</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>room_status_id</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>room_status.room_status_id</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Текущий статус</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>room_status_log — Состояние номера на дату: Журнал статусов: последний статус — текущее состояние номера</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>guest — Гость: Клиенты гостиницы</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="3" t="n"/>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>room_status_log</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор записи</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>guest_id</t>
+          <t>room_status_log</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>room_id</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>room.id</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1322,28 +1330,36 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор гостя</t>
+          <t>Номер</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>room_status_log</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>status_id</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>room_status.id</t>
+        </is>
+      </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1351,24 +1367,24 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Фамилия</t>
+          <t>Статус</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>room_status_log</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>status_date</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -1380,38 +1396,22 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Имя</t>
+          <t>Дата (пара номер + дата уникальна)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>middle_name</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Отчество</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>guest — Гость: Клиенты гостиницы</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1419,26 +1419,30 @@
           <t>guest</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>passport</t>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(11)</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Серия и номер паспорта</t>
+          <t>Идентификатор гостя</t>
         </is>
       </c>
     </row>
@@ -1450,141 +1454,157 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(18)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Телефон +7 (XXX) XXX-XX-XX</t>
+          <t>Фамилия</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>booking_status — Статус брони: Состояния брони</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="3" t="n"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Имя</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>booking_status</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>booking_status_id</t>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>patronymic</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор статуса</t>
+          <t>Отчество</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>booking_status</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR(30)</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Забронирован / Заселён / Выехал / Отменён</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>stay — Бронирование / заселение: Бронь и проживание гостя в номере: связь «многие ко многим» гость ↔ номер</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>booking — Бронирование / проживание: Бронь и проживание гостя в номере: связь «многие ко многим» гость ↔ номер</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="3" t="n"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>stay</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>booking</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>booking_id</t>
+          <t>stay</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>room_id</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>room.id</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1592,14 +1612,14 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор брони</t>
+          <t>Номер</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>booking</t>
+          <t>stay</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1609,7 +1629,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1619,7 +1639,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>guest.guest_id</t>
+          <t>guest.id</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1636,29 +1656,21 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>booking</t>
+          <t>stay</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>room_id</t>
+          <t>check_in</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>room.room_id</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1666,61 +1678,53 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Номер</t>
+          <t>Дата заезда</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>booking</t>
+          <t>stay</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>booking_status_id</t>
+          <t>check_out</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>booking_status.booking_status_id</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Статус брони</t>
+          <t>Дата выезда (не раньше заезда)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>booking</t>
+          <t>stay</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>check_in_date</t>
+          <t>is_checked_in</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr"/>
@@ -1732,24 +1736,24 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Дата заезда</t>
+          <t>FALSE — только бронь, TRUE — гость заехал</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>booking</t>
+          <t>stay</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>check_out_date</t>
+          <t>card_number</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
@@ -1761,80 +1765,84 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Дата выезда</t>
+          <t>Номер карты доступа</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>booking</t>
+          <t>stay</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>card_number</t>
+          <t>card_active</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Номер карты доступа</t>
+          <t>Карта активна (блокируется в 12:00 в день выезда)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>booking</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>is_card_active</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Карта активна (блокируется в 12:00 в день выезда)</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>payment — Оплата: Оплаты проживания (выручка для ADR и RevPAR)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>payment — Оплата: Оплаты проживания (выручка для ADR и RevPAR)</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="3" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор оплаты</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1842,22 +1850,26 @@
           <t>payment</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>payment_id</t>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>stay_id</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>stay.id</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1865,7 +1877,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор оплаты (номер квитанции)</t>
+          <t>За какое проживание</t>
         </is>
       </c>
     </row>
@@ -1877,24 +1889,16 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>booking_id</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>booking.booking_id</t>
-        </is>
-      </c>
+          <t>NUMERIC(10,2)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -1902,7 +1906,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>За какую бронь</t>
+          <t>Сумма, руб. (&gt; 0)</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1918,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>paid_at</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>NUMERIC(10,2)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1931,71 +1935,75 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Сумма, руб.</t>
+          <t>Дата и время оплаты</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>payment</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>paid_at</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>Дата и время оплаты</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>role — Роль: Роли пользователей ИС</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>cleaning_task — Уборка: График уборки номеров</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="3" t="n"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор роли</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>cleaning_task</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>cleaning_task_id</t>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>SERIAL</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr"/>
@@ -2006,73 +2014,45 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Идентификатор задания</t>
+          <t>Администратор / Пользователь</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>cleaning_task</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>room_id</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>room.room_id</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Номер</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>app_user — Пользователь: Пользователи ИС (сотрудники) — таблица «Пользователи»</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>cleaning_task</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>employee_id</t>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>INT IDENTITY</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>employee.employee_id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Да</t>
@@ -2080,24 +2060,24 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Горничная</t>
+          <t>Идентификатор пользователя</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>cleaning_task</t>
+          <t>app_user</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>cleaning_date</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -2109,24 +2089,24 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Дата уборки по графику</t>
+          <t>Фамилия</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>cleaning_task</t>
+          <t>app_user</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>is_done</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
@@ -2138,22 +2118,476 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Выполнено (номер → «Чистый»)</t>
+          <t>Имя</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>patronymic</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Отчество</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Логин</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>password_hash</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Хеш пароля</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>role_id</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>role.id</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>is_blocked</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Заблокирован (3 ошибки входа или месяц без входа)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>failed_attempts</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Неудачных попыток входа подряд</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>must_change_password</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Сменить выданный пароль при первом входе</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>last_login_at</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Последний успешный вход</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>app_user</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Когда создан</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>cleaning_task — Уборка: График уборки номеров</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>cleaning_task</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>INT IDENTITY</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор задания</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>cleaning_task</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>room_id</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>room.id</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Номер</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>cleaning_task</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>app_user_id</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>app_user.id</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Сотрудник</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>cleaning_task</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>task_date</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Дата уборки по графику</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>cleaning_task</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>is_done</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A48:G48"/>
+  <mergeCells count="13">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2166,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2188,48 +2622,72 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>role (Роль)</t>
+          <t>floor (Этаж)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Администратор; Руководитель; Горничная</t>
+          <t>1; 2; 3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>room_category (Категория номера)</t>
+          <t>comfort_class (Класс комфорта)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Одноместный стандарт; Одноместный эконом; Стандарт двухместный с 2 раздельными кроватями; Эконом двухместный с 2 раздельными кроватями; 3-местный бюджет; Бизнес с 1 или 2 кроватями; Двухкомнатный двухместный стандарт с 1 или 2 кроватями; Студия; Люкс с 2 двуспальными кроватями</t>
+          <t>Стандарт; Эконом; Бюджет; Бизнес; Студия; Люкс</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>room_status (Статус номера)</t>
+          <t>bed_type (Тип кроватей)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Чистый; Занят; Грязный; Назначен к уборке</t>
+          <t>2 раздельные кровати (2–2); 1 или 2 кровати (1–2); 2 двуспальные кровати (2–2)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>booking_status (Статус брони)</t>
+          <t>room_category (Категория номера)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Забронирован; Заселён; Выехал; Отменён</t>
+          <t>Одноместный стандарт; Одноместный эконом; Стандарт двухместный с 2 раздельными кроватями; Эконом двухместный с 2 раздельными кроватями; 3-местный бюджет; Бизнес с 1 или 2 кроватями; Двухкомнатный двухместный стандарт с 1 или 2 кроватями; Студия; Люкс с 2 двуспальными кроватями</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>room_status (Статус номера)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Занят; Чистый; Назначен к уборке; Грязный</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>role (Роль)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Администратор; Пользователь</t>
         </is>
       </c>
     </row>
